--- a/build/assets/Images/image_manifest.xlsx
+++ b/build/assets/Images/image_manifest.xlsx
@@ -558,7 +558,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>page 10 · चम्मच; page 14 · round 2 चम्मच</t>
+          <t>page 13 · चम्मच; page 14 · round 2 चम्मच</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>page 9 · चाँद; page 13 · चाँद; page 14 · round 2 चाँद</t>
+          <t>page 11 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>page 13 · चश्मा</t>
+          <t>page 11 · चश्मा</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>page 11 · चिड़िया</t>
+          <t>page 10 · चिड़िया</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>page 2 · picture; page 10 · चूहा; page 14 · round 2 चूहा</t>
+          <t>page 2 · picture; page 13 · चूहा; page 14 · round 2 चूहा</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>page 13 · लाल; page 14 · round 1 refill लाल</t>
+          <t>page 11 · लाल; page 14 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>page 11 · लड्डू</t>
+          <t>page 10 · लड्डू</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>page 13 · माला; page 14 · round 1 refill माला</t>
+          <t>page 11 · माला; page 14 · round 1 refill माला</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>page 11 · मामा</t>
+          <t>page 10 · मामा</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>page 4 · picture; page 11 · मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · picture; page 10 · मूली; page 14 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>page 10 · पानी; page 14 · round 1 पानी</t>
+          <t>page 13 · पानी; page 14 · round 1 पानी</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>page 7 · पतंग; page 9 · पतंग; page 14 · round 1 पतंग</t>
+          <t>page 7 · पतंग; page 12 · पतंग; page 14 · round 1 पतंग</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>page 10 · पायल</t>
+          <t>page 13 · पायल</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">

--- a/build/assets/Images/image_manifest.xlsx
+++ b/build/assets/Images/image_manifest.xlsx
@@ -593,7 +593,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>page 11 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
+          <t>page 9 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>page 11 · चश्मा</t>
+          <t>page 9 · चश्मा</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>page 10 · चिड़िया</t>
+          <t>page 8 · चिड़िया</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>page 11 · लाल; page 14 · round 1 refill लाल</t>
+          <t>page 9 · लाल; page 14 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>page 10 · लड्डू</t>
+          <t>page 8 · लड्डू</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>page 11 · माला; page 14 · round 1 refill माला</t>
+          <t>page 9 · माला; page 14 · round 1 refill माला</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>page 10 · मामा</t>
+          <t>page 8 · मामा</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>page 4 · picture; page 10 · मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · picture; page 8 · मूली; page 14 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">

--- a/build/assets/Images/image_manifest.xlsx
+++ b/build/assets/Images/image_manifest.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -513,17 +513,13 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>obj_aam</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>आम</t>
-        </is>
-      </c>
+          <t>cover_hero</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>page 7 · आम; page 14 · round 1 आम; page 14 · round 2 refill आम</t>
+          <t>engine/shared</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -533,12 +529,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>349x333</t>
+          <t>1400x594</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>776</t>
         </is>
       </c>
     </row>
@@ -548,17 +544,17 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>obj_chammach</t>
+          <t>obj_aam</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>चम्मच</t>
+          <t>आम</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>page 13 · चम्मच; page 14 · round 2 चम्मच</t>
+          <t>page 7 · आम; page 14 · round 1 आम; page 14 · round 2 refill आम</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -568,12 +564,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>189x512</t>
+          <t>349x333</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -583,17 +579,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>obj_chand</t>
+          <t>obj_chammach</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>चाँद</t>
+          <t>चम्मच</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>page 9 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
+          <t>page 13 · चम्मच; page 14 · round 2 चम्मच</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -603,12 +599,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>259x284</t>
+          <t>189x512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>95</t>
         </is>
       </c>
     </row>
@@ -618,17 +614,17 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>obj_chashma</t>
+          <t>obj_chand</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>चश्मा</t>
+          <t>चाँद</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>page 9 · चश्मा</t>
+          <t>page 9 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -638,12 +634,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>512x377</t>
+          <t>259x284</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -653,17 +649,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>obj_chidiya</t>
+          <t>obj_chashma</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>चिड़िया</t>
+          <t>चश्मा</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>page 8 · चिड़िया</t>
+          <t>page 9 · चश्मा</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -673,12 +669,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512x508</t>
+          <t>512x377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -688,17 +684,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>obj_chinti</t>
+          <t>obj_chidiya</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>चींटी</t>
+          <t>चिड़िया</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 चींटी</t>
+          <t>page 8 · चिड़िया</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -708,12 +704,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>720x758</t>
+          <t>512x508</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>265</t>
         </is>
       </c>
     </row>
@@ -723,17 +719,17 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>obj_chuha</t>
+          <t>obj_chinti</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>चूहा</t>
+          <t>चींटी</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>page 2 · picture; page 13 · चूहा; page 14 · round 2 चूहा</t>
+          <t>page 14 · round 2 चींटी</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -743,12 +739,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>348x374</t>
+          <t>720x758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>262</t>
         </is>
       </c>
     </row>
@@ -758,17 +754,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>obj_ghar</t>
+          <t>obj_chuha</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>घर</t>
+          <t>चूहा</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 घर; page 14 · round 2 refill घर</t>
+          <t>page 2 · picture; page 13 · चूहा; page 14 · round 2 चूहा</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -778,12 +774,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>422x327</t>
+          <t>348x374</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -793,17 +789,17 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>obj_kabutar</t>
+          <t>obj_ghar</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>कबूतर</t>
+          <t>घर</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 कबूतर</t>
+          <t>page 14 · round 1 घर; page 14 · round 2 refill घर</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -813,12 +809,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>512x504</t>
+          <t>422x327</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -828,17 +824,17 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>obj_kamal</t>
+          <t>obj_kabutar</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>कमल</t>
+          <t>कबूतर</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 कमल</t>
+          <t>page 14 · round 2 कबूतर</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -848,12 +844,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>512x404</t>
+          <t>512x504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -863,17 +859,17 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>obj_kauaa</t>
+          <t>obj_kamal</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>कौआ</t>
+          <t>कमल</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>cover · picture; page 14 · round 2 कौआ</t>
+          <t>page 14 · round 2 कमल</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -883,12 +879,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>467x512</t>
+          <t>512x404</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -898,17 +894,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>obj_kela</t>
+          <t>obj_kauaa</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>केला</t>
+          <t>कौआ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>page 7 · केला; page 14 · round 1 केला; page 14 · round 2 केला</t>
+          <t>cover · picture; page 14 · round 2 कौआ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -918,12 +914,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>381x391</t>
+          <t>467x512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -933,17 +929,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>obj_laal</t>
+          <t>obj_kela</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>लाल</t>
+          <t>केला</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>page 9 · लाल; page 14 · round 1 refill लाल</t>
+          <t>page 7 · केला; page 14 · round 1 केला; page 14 · round 2 केला</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -953,12 +949,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>797x820</t>
+          <t>381x391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>82</t>
         </is>
       </c>
     </row>
@@ -968,17 +964,17 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>obj_laddu</t>
+          <t>obj_laal</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>लड्डू</t>
+          <t>लाल</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>page 8 · लड्डू</t>
+          <t>page 9 · लाल; page 14 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -988,12 +984,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>512x379</t>
+          <t>797x820</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>326</t>
         </is>
       </c>
     </row>
@@ -1003,17 +999,17 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>obj_machhli</t>
+          <t>obj_laddu</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>मछली</t>
+          <t>लड्डू</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 मछली; page 14 · round 2 refill मछली</t>
+          <t>page 8 · लड्डू</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1023,12 +1019,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>423x319</t>
+          <t>512x379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>272</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1034,17 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>obj_mala</t>
+          <t>obj_machhli</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>माला</t>
+          <t>मछली</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>page 9 · माला; page 14 · round 1 refill माला</t>
+          <t>page 14 · round 1 मछली; page 14 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1058,12 +1054,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>534x333</t>
+          <t>423x319</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -1073,17 +1069,17 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>obj_mama</t>
+          <t>obj_mala</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>मामा</t>
+          <t>माला</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>page 8 · मामा</t>
+          <t>page 9 · माला; page 14 · round 1 refill माला</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>807x859</t>
+          <t>534x333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>155</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1104,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>obj_muli</t>
+          <t>obj_mama</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>मूली</t>
+          <t>मामा</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>page 4 · picture; page 8 · मूली; page 14 · round 1 refill मूली</t>
+          <t>page 8 · मामा</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1128,12 +1124,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>460x680</t>
+          <t>807x859</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>278</t>
         </is>
       </c>
     </row>
@@ -1143,17 +1139,17 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>obj_pani</t>
+          <t>obj_muli</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>पानी</t>
+          <t>मूली</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>page 13 · पानी; page 14 · round 1 पानी</t>
+          <t>page 4 · picture; page 8 · मूली; page 14 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1163,12 +1159,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261x349</t>
+          <t>460x680</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>208</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1174,17 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>obj_papita</t>
+          <t>obj_pani</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>पपीता</t>
+          <t>पानी</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>page 6 · picture; page 7 · पपीता; page 14 · round 1 पपीता</t>
+          <t>page 13 · पानी; page 14 · round 1 पानी</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1198,12 +1194,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1403x1444</t>
+          <t>261x349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>109</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1209,17 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>obj_patang</t>
+          <t>obj_papita</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>पतंग</t>
+          <t>पपीता</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>page 7 · पतंग; page 12 · पतंग; page 14 · round 1 पतंग</t>
+          <t>page 6 · picture; page 7 · पपीता; page 14 · round 1 पपीता</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1233,12 +1229,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>381x384</t>
+          <t>1403x1444</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>945</t>
         </is>
       </c>
     </row>
@@ -1248,17 +1244,17 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>obj_patta</t>
+          <t>obj_patang</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>पत्ता</t>
+          <t>पतंग</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 पत्ता</t>
+          <t>page 7 · पतंग; page 12 · पतंग; page 14 · round 1 पतंग</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1268,12 +1264,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>414x393</t>
+          <t>381x384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>93</t>
         </is>
       </c>
     </row>
@@ -1283,51 +1279,86 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>obj_patta</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>पत्ता</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>page 14 · round 1 पत्ता</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>414x393</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>obj_payal</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>पायल</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>page 13 · पायल</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>349x299</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>One row per picture the card references. 'Used by' is where the child sees it.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Pink MISSING = the card asks for this image and no file exists; the build's own guard would not catch it, the page would simply fall back to an emoji.</t>
+          <t>One row per picture the card references. 'Used by' is where the child sees it.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Pink MISSING = the card asks for this image and no file exists; the build's own guard would not catch it, the page would simply fall back to an emoji.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>For NEW art: transparent PNG, long edge 512px, no baked background. The existing set is not uniform (284-1444px long edge, 7 of 23 at 512) - it grew over several rounds, and the engine fits each picture to its tile, so size is a delivery convention here rather than something the game depends on.</t>
         </is>

--- a/build/assets/Images/image_manifest.xlsx
+++ b/build/assets/Images/image_manifest.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>cover · picture; page 14 · round 2 कौआ</t>
+          <t>page 14 · round 2 कौआ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">

--- a/build/assets/Images/image_manifest.xlsx
+++ b/build/assets/Images/image_manifest.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>page 7 · आम; page 14 · round 1 आम; page 14 · round 2 refill आम</t>
+          <t>page 7 · आम; page 13 · round 1 आम; page 13 · round 2 refill आम</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>page 13 · चम्मच; page 14 · round 2 चम्मच</t>
+          <t>page 13 · round 2 चम्मच</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>page 9 · चाँद; page 12 · चाँद; page 14 · round 2 चाँद</t>
+          <t>page 9 · चाँद; page 12 · चाँद; page 13 · round 2 चाँद</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 चींटी</t>
+          <t>page 13 · round 2 चींटी</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>page 2 · picture; page 13 · चूहा; page 14 · round 2 चूहा</t>
+          <t>page 2 · picture; page 13 · round 2 चूहा</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 घर; page 14 · round 2 refill घर</t>
+          <t>page 13 · round 1 घर; page 13 · round 2 refill घर</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 कबूतर</t>
+          <t>page 13 · round 2 कबूतर</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 कमल</t>
+          <t>page 13 · round 2 कमल</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 2 कौआ</t>
+          <t>page 13 · round 2 कौआ</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>page 7 · केला; page 14 · round 1 केला; page 14 · round 2 केला</t>
+          <t>page 7 · केला; page 13 · round 1 केला; page 13 · round 2 केला</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>page 9 · लाल; page 14 · round 1 refill लाल</t>
+          <t>page 9 · लाल; page 13 · round 1 refill लाल</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 मछली; page 14 · round 2 refill मछली</t>
+          <t>page 13 · round 1 मछली; page 13 · round 2 refill मछली</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>page 9 · माला; page 14 · round 1 refill माला</t>
+          <t>page 9 · माला; page 13 · round 1 refill माला</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>page 4 · picture; page 8 · मूली; page 14 · round 1 refill मूली</t>
+          <t>page 4 · picture; page 8 · मूली; page 13 · round 1 refill मूली</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>page 13 · पानी; page 14 · round 1 पानी</t>
+          <t>page 13 · round 1 पानी</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>page 6 · picture; page 7 · पपीता; page 14 · round 1 पपीता</t>
+          <t>page 6 · picture; page 7 · पपीता; page 13 · round 1 पपीता</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>page 7 · पतंग; page 12 · पतंग; page 14 · round 1 पतंग</t>
+          <t>page 7 · पतंग; page 12 · पतंग; page 13 · round 1 पतंग</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>page 14 · round 1 पत्ता</t>
+          <t>page 13 · round 1 पत्ता</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1317,14 +1317,10 @@
           <t>obj_payal</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>पायल</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>page 13 · पायल</t>
+          <t>engine/shared</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
